--- a/02-formulas-functions/06-lookup-functions/2.6-lookup-functions.xlsx
+++ b/02-formulas-functions/06-lookup-functions/2.6-lookup-functions.xlsx
@@ -20225,7 +20225,7 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>Encounter ENC110900 is on row 9 of the Encounters sheet. Use VLOOKUP with its PatientID (cell B9) to return the patient's last name from the Patients sheet.</t>
+          <t>Encounter ENC110900 is on row 9 of the Encounters sheet. Use VLOOKUP with its PatientID (cell Encounters!B9) to return the patient's last name from the Patients sheet.</t>
         </is>
       </c>
       <c r="C5" s="44" t="inlineStr">
@@ -20831,7 +20831,7 @@
           <t>ENC119O88 contains the letter O where the real ID ENC119088 has a zero. To Excel they're different text, so every lookup comes back empty-handed. That's the most common reason a lookup fails on data that looks right. The sample solution shown is row 6. Three techniques make the whole card fail politely:
 1. Every XLOOKUP gets an if_not_found of "Not found".
 2. Chained lookups pass "Not found" along. The inner XLOOKUP returns it, and the outer one can't find a DxCode called "Not found", so it returns its own "Not found".
-3. Rows that calculate (the name join and DATEDIF) test the helper cell first with IF(B6="Not found","Not found",…), because DATEDIF of a text value would return #VALUE!.
+3. Rows that join or calculate (the two name rows and the age row) test their helper cell first with IF(B6="Not found","Not found",…). Without that test, DATEDIF of the text "Not found" returns #VALUE!. A name join would show #N/A, or "Not found Not found" if each of its lookups had its own if_not_found.
 Your finished card should match this:
 | Row | Field | Card A (ENC117295) | Card B (ENC119O88) |
 |:-:|---|---|---|
@@ -20892,10 +20892,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="34" customHeight="1">
+    <row r="2" ht="49" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>The Encounters sheet stores IDs only. Every answer comes from looking an ID up in another sheet. Write each answer as a formula. Lock lookup ranges with $ (F4, Mac: ⌘ + T) so they don't slide when you copy.</t>
+          <t>The Encounters sheet stores IDs only. Every answer comes from looking an ID up in another sheet. Write each answer as a formula. Your answers sit on this Practice sheet, so a reference to a data cell needs its sheet name, such as Encounters!B9. Click the cell on the data sheet and Excel writes the sheet name for you. Lock lookup ranges with $ (F4, Mac: ⌘ + T) so they don't slide when you copy.</t>
         </is>
       </c>
     </row>
@@ -20947,7 +20947,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>Encounter ENC110900 is on row 9 of the Encounters sheet. Use VLOOKUP with its PatientID (cell B9) to return the patient's last name from the Patients sheet.</t>
+          <t>Encounter ENC110900 is on row 9 of the Encounters sheet. Use VLOOKUP with its PatientID (cell Encounters!B9) to return the patient's last name from the Patients sheet.</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">

--- a/02-formulas-functions/06-lookup-functions/2.6-lookup-functions.xlsx
+++ b/02-formulas-functions/06-lookup-functions/2.6-lookup-functions.xlsx
@@ -227,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -311,6 +311,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -904,7 +907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C42"/>
+  <dimension ref="B2:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1077,11 +1080,11 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>MRN is stored as 8-character TEXT on purpose (leading zeros matter). The green triangles in that column are Excel's 'number stored as text' warning; leave them as they are.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="33" customHeight="1">
+          <t>MRN is stored as 8-character TEXT on purpose (leading zeros matter). The green triangles in that column are Excel's 'number stored as text' warning. Leave them as they are.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
       <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Note</t>
@@ -1089,237 +1092,249 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
+          <t>Every data sheet is an Excel Table. When you drag over a data sheet's column while typing a formula, Excel may write a Table reference such as tblPatients[LastName] instead of Patients!D2:D186. Both give the same result (Lesson 3.1 covers Tables).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="33" customHeight="1">
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
           <t>BMI = 703 × WeightLb ÷ HeightIn², rounded to 1 decimal place. Age is the patient's age in completed years on 12/31/2025.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="B21" s="8" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>The Card sheet is for the bonus challenge.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Color legend</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="B24" s="9" t="inlineStr">
+      <c r="C24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Yellow cell</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>Your answer goes here.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="10" t="inlineStr">
+    <row r="26" ht="18" customHeight="1">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>Gray cell</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Pre-filled summary formula — it reads the work you did on another sheet.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="11" t="inlineStr">
+    <row r="27" ht="18" customHeight="1">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>✔ Correct</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Your answer matches the key.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="B27" s="12" t="inlineStr">
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>✘ Not yet</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Not matching yet — check the hint and try again.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Sheets in this workbook</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Encounters</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Data: 529 rows — Excel Table 'tblEncounters'</t>
-        </is>
-      </c>
+      <c r="C30" s="5" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Patients</t>
+          <t>Encounters</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Data: 185 rows — Excel Table 'tblPatients'</t>
+          <t>Data: 529 rows — Excel Table 'tblEncounters'</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>Patients</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Data: 24 rows — Excel Table 'tblReferrals'</t>
+          <t>Data: 185 rows — Excel Table 'tblPatients'</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Providers</t>
+          <t>Referrals</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Data: 147 rows — Excel Table 'tblProviders'</t>
+          <t>Data: 24 rows — Excel Table 'tblReferrals'</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Diagnoses</t>
+          <t>Providers</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Data: 51 rows — Excel Table 'tblDiagnoses'</t>
+          <t>Data: 147 rows — Excel Table 'tblProviders'</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Payers</t>
+          <t>Diagnoses</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Data: 8 rows — Excel Table 'tblPayers'</t>
+          <t>Data: 51 rows — Excel Table 'tblDiagnoses'</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Departments</t>
+          <t>Payers</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Data: 31 rows — Excel Table 'tblDepartments'</t>
+          <t>Data: 8 rows — Excel Table 'tblPayers'</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Claims</t>
+          <t>Departments</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Data: 529 rows — Excel Table 'tblClaims'</t>
+          <t>Data: 31 rows — Excel Table 'tblDepartments'</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Budget</t>
+          <t>Claims</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Data: 31 rows — Excel Table 'tblBudget'</t>
+          <t>Data: 529 rows — Excel Table 'tblClaims'</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>BMITiers</t>
+          <t>Budget</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Data: 6 rows — Excel Table 'tblBMITiers'</t>
+          <t>Data: 31 rows — Excel Table 'tblBudget'</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="8" t="inlineStr">
         <is>
+          <t>BMITiers</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Data: 6 rows — Excel Table 'tblBMITiers'</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
           <t>AgeBands</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>Data: 6 rows — Excel Table 'tblAgeBands'</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="63" customHeight="1">
-      <c r="B41" s="8" t="inlineStr">
+    <row r="42" ht="63" customHeight="1">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>About the data</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>Every 2025 encounter (529) for the 185 patients on Dr. Isabella Nguyen's internal medicine panel, stored as IDs only, plus the lookup tables that turn those IDs into names: the panel roster, providers, ICD-10 diagnoses, payers, departments, and claims. Also a 2025 department budget grid, BMI and age-band tier tables, and the practice's December 2025 referral list.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="B42" s="8" t="inlineStr">
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>
@@ -18246,13 +18261,13 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19739,10 +19754,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="79" customHeight="1">
+    <row r="2" ht="124" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Dr. Nguyen's care manager answers the same questions all day: who is this encounter's patient, how old were they, what were they treated for, who was the attending, who pays, and where does the claim stand? Build a reusable lookup card on the Card sheet. Each column takes one EncounterID in row 5 and returns ten facts below it. Rows 6 and 7 are helper cells (PatientID and Attending ProviderID) that the other rows can reuse. Write every formula in column B, then copy B6:B15 to C6:C15. Card A holds ENC117295. Card B holds ENC119O88, an ID copied from a handwritten note, and every row of Card B must show Not found instead of an error. Keep both IDs in place while you check your answers. The gray cells on the Bonus sheet read your card.</t>
+          <t>Dr. Nguyen's care manager answers the same questions all day: who is this encounter's patient, how old were they, what were they treated for, who was the attending, who pays, and where does the claim stand? Build a reusable lookup card on the Card sheet. Each card is one column: it takes an EncounterID in row 5 and returns ten facts in rows 6 to 15. Rows 6 and 7 are helper cells (PatientID and Attending ProviderID) that the other rows reuse. Card 1 (column B) holds ENC117295. Card 2 (column C) holds ENC119O88, an ID copied from a handwritten note, and every row of Card 2 must show Not found instead of an error. Write every formula in column B, then copy B6:B15 and paste it into C6:C15. Refer to the ID as B$5, with no $ before the B, so it becomes C$5 in column C. The $ before the 5 keeps it on row 5 if you copy a formula down to start the next row. Use Copy (Ctrl + C, Mac: ⌘ + C) and Paste (Ctrl + V, Mac: ⌘ + V) rather than dragging the fill handle, because dragging to the right shifts Table references such as tblEncounters[PatientID] to the next Table column. Keep both IDs in place while you check your answers. The gray cells on the Bonus sheet read your card.</t>
         </is>
       </c>
     </row>
@@ -19794,12 +19809,12 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>Card A (ENC117295): what does your Patient name row (Card!B8) show? Format: First Last.</t>
+          <t>Card 1 (ENC117295): what does your Patient name row (Card!B8) show? Format: First Last.</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>Chain two lookups: EncounterID → PatientID (row 6), then PatientID → names. Join with &amp;" "&amp;</t>
+          <t>Chain two lookups: first EncounterID to PatientID (row 6), then PatientID to the names. Join them with &amp;" "&amp;</t>
         </is>
       </c>
       <c r="D6" cm="1" s="34">
@@ -19819,7 +19834,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Card A: how old was the patient, in completed years, on the encounter's AdmitDate (Card!B9)?</t>
+          <t>Card 1: how old was the patient, in completed years, on the encounter's AdmitDate (Card!B9)?</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -19844,7 +19859,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Card A: what does your Attending row (Card!B12) show? Format: First Last, Credential (for example, Isabella Nguyen, MD).</t>
+          <t>Card 1: what does your Attending row (Card!B12) show? Format: First Last, Credential (for example, Isabella Nguyen, MD).</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -19869,7 +19884,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Card A: what is the claim status (Card!B15)? Claims are matched by EncounterID, which is column B of the Claims sheet.</t>
+          <t>Card 1: what is the claim status (Card!B15)? Claims are matched by EncounterID, which is column B of the Claims sheet.</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -19894,7 +19909,7 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>Card B (ENC119O88): how many of the ten output rows (Card!C6:C15) show exactly Not found? All ten should. If any shows #N/A or #VALUE!, fix that row's formula in column B and copy it right again.</t>
+          <t>Card 2 (ENC119O88): how many of the ten output rows (Card!C6:C15) show exactly Not found? All ten should. If any shows #N/A or #VALUE!, fix that row's formula in column B and copy it to column C again.</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -19941,8 +19956,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -19953,10 +19968,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="34" customHeight="1">
+    <row r="2" ht="48" customHeight="1">
       <c r="A2" s="35" t="inlineStr">
         <is>
-          <t>Type one formula in each yellow cell of column B (B6:B15), then copy B6:B15 to C6:C15. Don't put a $ in front of the B when you refer to B5, so the reference becomes C5 when you copy right. Every Card B cell must show Not found. The gray cells on the Bonus sheet check your card.</t>
+          <t>Type one formula in each yellow cell of column B (B6:B15) and refer to the ID as B$5. Then copy B6:B15 (Ctrl + C, Mac: ⌘ + C) and paste it into C6:C15 (Ctrl + V, Mac: ⌘ + V). B$5 becomes C$5, and Copy and Paste keeps Table references such as tblEncounters[PatientID] on the same column (dragging the fill handle to the right would shift them). Every Card 2 cell must show Not found. The gray cells on the Bonus sheet check your card.</t>
         </is>
       </c>
     </row>
@@ -19968,12 +19983,12 @@
       </c>
       <c r="B4" s="36" t="inlineStr">
         <is>
-          <t>Card A</t>
+          <t>Card 1</t>
         </is>
       </c>
       <c r="C4" s="36" t="inlineStr">
         <is>
-          <t>Card B</t>
+          <t>Card 2</t>
         </is>
       </c>
       <c r="D4" s="36" t="inlineStr">
@@ -20000,7 +20015,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Input: keep these two IDs while you check the bonus</t>
+          <t>Input: keep both IDs while you check the bonus</t>
         </is>
       </c>
     </row>
@@ -20052,8 +20067,8 @@
           <t>Age at admission (years)</t>
         </is>
       </c>
-      <c r="B9" s="39" t="n"/>
-      <c r="C9" s="39" t="n"/>
+      <c r="B9" s="41" t="n"/>
+      <c r="C9" s="41" t="n"/>
       <c r="D9" s="40" t="inlineStr">
         <is>
           <t>Patients DOB + Encounters AdmitDate</t>
@@ -20172,46 +20187,46 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="41" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>🔑 Answer Key — Lesson 2.6</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="42" t="inlineStr">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="44" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
+      <c r="D4" s="44" t="inlineStr">
         <is>
           <t>Sample solution</t>
         </is>
       </c>
-      <c r="E4" s="43" t="inlineStr">
+      <c r="E4" s="44" t="inlineStr">
         <is>
           <t>Live result</t>
         </is>
       </c>
-      <c r="F4" s="43" t="inlineStr">
+      <c r="F4" s="44" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -20228,17 +20243,17 @@
           <t>Encounter ENC110900 is on row 9 of the Encounters sheet. Use VLOOKUP with its PatientID (cell Encounters!B9) to return the patient's last name from the Patients sheet.</t>
         </is>
       </c>
-      <c r="C5" s="44" t="inlineStr">
+      <c r="C5" s="45" t="inlineStr">
         <is>
           <t>Robertson</t>
         </is>
       </c>
-      <c r="D5" s="45" t="inlineStr">
+      <c r="D5" s="46" t="inlineStr">
         <is>
           <t>=VLOOKUP(Encounters!B9,Patients!$A$2:$K$186,4,FALSE)</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="46">
+      <c r="E5" cm="1" s="47">
         <f t="array" ref="E5">VLOOKUP(Encounters!B9,Patients!$A$2:$K$186,4,FALSE)</f>
         <v/>
       </c>
@@ -20259,17 +20274,17 @@
           <t>Encounter ENC111256 (Encounters row 20) was billed to payer PY02. Use VLOOKUP on the Payers sheet to return the payer's PayerType.</t>
         </is>
       </c>
-      <c r="C6" s="44" t="inlineStr">
+      <c r="C6" s="45" t="inlineStr">
         <is>
           <t>Medicare Advantage</t>
         </is>
       </c>
-      <c r="D6" s="45" t="inlineStr">
+      <c r="D6" s="46" t="inlineStr">
         <is>
           <t>=VLOOKUP(Encounters!I20,Payers!$A$2:$F$9,3,FALSE)</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="46">
+      <c r="E6" cm="1" s="47">
         <f t="array" ref="E6">VLOOKUP(Encounters!I20,Payers!$A$2:$F$9,3,FALSE)</f>
         <v/>
       </c>
@@ -20290,17 +20305,17 @@
           <t>Encounter ENC113996 (Encounters row 150) has primary diagnosis code E11.65. Use XLOOKUP to return its description from the Diagnoses sheet.</t>
         </is>
       </c>
-      <c r="C7" s="44" t="inlineStr">
+      <c r="C7" s="45" t="inlineStr">
         <is>
           <t>Type 2 diabetes mellitus with hyperglycemia</t>
         </is>
       </c>
-      <c r="D7" s="45" t="inlineStr">
+      <c r="D7" s="46" t="inlineStr">
         <is>
           <t>=XLOOKUP(Encounters!H150,Diagnoses!$A$2:$A$52,Diagnoses!$B$2:$B$52)</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="46">
+      <c r="E7" cm="1" s="47">
         <f t="array" ref="E7">_xlfn.XLOOKUP(Encounters!H150,Diagnoses!$A$2:$A$52,Diagnoses!$B$2:$B$52)</f>
         <v/>
       </c>
@@ -20321,17 +20336,17 @@
           <t>Who attended encounter ENC112339 (Encounters row 73)? Use INDEX and MATCH with its AttendingProviderID to return the provider's Specialty from the Providers sheet.</t>
         </is>
       </c>
-      <c r="C8" s="44" t="inlineStr">
+      <c r="C8" s="45" t="inlineStr">
         <is>
           <t>Pulmonary &amp; Critical Care</t>
         </is>
       </c>
-      <c r="D8" s="45" t="inlineStr">
+      <c r="D8" s="46" t="inlineStr">
         <is>
           <t>=INDEX(Providers!$E$2:$E$148,MATCH(Encounters!G73,Providers!$A$2:$A$148,0))</t>
         </is>
       </c>
-      <c r="E8" cm="1" s="46">
+      <c r="E8" cm="1" s="47">
         <f t="array" ref="E8">INDEX(Providers!$E$2:$E$148,MATCH(Encounters!G73,Providers!$A$2:$A$148,0))</f>
         <v/>
       </c>
@@ -20352,15 +20367,15 @@
           <t>Fill the yellow PayerName column on the Encounters sheet with a lookup that returns each encounter's payer name (start in K2 and copy down to row 530). The gray cell counts how many encounters your column shows as exactly "Medicare".</t>
         </is>
       </c>
-      <c r="C9" s="44" t="n">
+      <c r="C9" s="45" t="n">
         <v>120</v>
       </c>
-      <c r="D9" s="45" t="inlineStr">
+      <c r="D9" s="46" t="inlineStr">
         <is>
           <t>=XLOOKUP(I2,Payers!$A$2:$A$9,Payers!$B$2:$B$9)</t>
         </is>
       </c>
-      <c r="E9" cm="1" s="46">
+      <c r="E9" cm="1" s="47">
         <f t="array" ref="E9">COUNTIF(Encounters!$I$2:$I$530,"PY01")</f>
         <v/>
       </c>
@@ -20381,17 +20396,17 @@
           <t>Patient PT10395 is on Patients row 21, and the Age column shows 75. Use VLOOKUP with an approximate match (TRUE) on the AgeBands sheet to return the patient's age band.</t>
         </is>
       </c>
-      <c r="C10" s="44" t="inlineStr">
+      <c r="C10" s="45" t="inlineStr">
         <is>
           <t>75-84</t>
         </is>
       </c>
-      <c r="D10" s="45" t="inlineStr">
+      <c r="D10" s="46" t="inlineStr">
         <is>
           <t>=VLOOKUP(Patients!G21,AgeBands!$A$2:$B$7,2,TRUE)</t>
         </is>
       </c>
-      <c r="E10" cm="1" s="46">
+      <c r="E10" cm="1" s="47">
         <f t="array" ref="E10">VLOOKUP(Patients!G21,AgeBands!$A$2:$B$7,2,TRUE)</f>
         <v/>
       </c>
@@ -20412,15 +20427,15 @@
           <t>Fill the yellow BMICategory column on the Patients sheet: look up each patient's BMI in the BMITiers table with an approximate match (start in L2 and copy down to row 186). The gray cell counts patients in any obesity class (BMI 30 or higher).</t>
         </is>
       </c>
-      <c r="C11" s="44" t="n">
+      <c r="C11" s="45" t="n">
         <v>82</v>
       </c>
-      <c r="D11" s="45" t="inlineStr">
+      <c r="D11" s="46" t="inlineStr">
         <is>
           <t>=VLOOKUP(J2,BMITiers!$A$2:$B$7,2,TRUE)</t>
         </is>
       </c>
-      <c r="E11" cm="1" s="46">
+      <c r="E11" cm="1" s="47">
         <f t="array" ref="E11">COUNTIF(Patients!$J$2:$J$186,"&gt;=30")</f>
         <v/>
       </c>
@@ -20441,17 +20456,17 @@
           <t>The lab's interface file sent a result for MRN 50339. It arrived as a number, so its leading zeros were dropped, but the Patients sheet stores MRNs as 8-character text. Return the PatientID for this MRN. (PatientID is to the left of MRN, so VLOOKUP can't do it.)</t>
         </is>
       </c>
-      <c r="C12" s="44" t="inlineStr">
+      <c r="C12" s="45" t="inlineStr">
         <is>
           <t>PT11047</t>
         </is>
       </c>
-      <c r="D12" s="45" t="inlineStr">
+      <c r="D12" s="46" t="inlineStr">
         <is>
           <t>=XLOOKUP(TEXT(50339,"00000000"),Patients!$B$2:$B$186,Patients!$A$2:$A$186)</t>
         </is>
       </c>
-      <c r="E12" cm="1" s="46">
+      <c r="E12" cm="1" s="47">
         <f t="array" ref="E12">_xlfn.XLOOKUP(TEXT(50339,"00000000"),Patients!$B$2:$B$186,Patients!$A$2:$A$186)</f>
         <v/>
       </c>
@@ -20472,17 +20487,17 @@
           <t>A clinic note mentions "osteoarthritis of the right knee." Use a wildcard lookup to return the DxCode whose DxDescription contains the word knee.</t>
         </is>
       </c>
-      <c r="C13" s="44" t="inlineStr">
+      <c r="C13" s="45" t="inlineStr">
         <is>
           <t>M17.11</t>
         </is>
       </c>
-      <c r="D13" s="45" t="inlineStr">
+      <c r="D13" s="46" t="inlineStr">
         <is>
           <t>=XLOOKUP("*knee*",Diagnoses!$B$2:$B$52,Diagnoses!$A$2:$A$52,,2)</t>
         </is>
       </c>
-      <c r="E13" cm="1" s="46">
+      <c r="E13" cm="1" s="47">
         <f t="array" ref="E13">_xlfn.XLOOKUP("*knee*",Diagnoses!$B$2:$B$52,Diagnoses!$A$2:$A$52,,2)</f>
         <v/>
       </c>
@@ -20503,15 +20518,15 @@
           <t>Two-way lookup: on the Budget sheet, what is the 2025 Pharmaceuticals budget for department D130 (Intensive Care Unit at Bluestone Memorial Hospital)? Find the row by DeptID and the column by category name.</t>
         </is>
       </c>
-      <c r="C14" s="47" t="n">
+      <c r="C14" s="48" t="n">
         <v>993601</v>
       </c>
-      <c r="D14" s="45" t="inlineStr">
+      <c r="D14" s="46" t="inlineStr">
         <is>
           <t>=INDEX(Budget!$D$2:$J$32,MATCH("D130",Budget!$A$2:$A$32,0),MATCH("Pharmaceuticals",Budget!$D$1:$J$1,0))</t>
         </is>
       </c>
-      <c r="E14" cm="1" s="48">
+      <c r="E14" cm="1" s="49">
         <f t="array" ref="E14">INDEX(Budget!$D$2:$J$32,MATCH("D130",Budget!$A$2:$A$32,0),MATCH("Pharmaceuticals",Budget!$D$1:$J$1,0))</f>
         <v/>
       </c>
@@ -20532,15 +20547,15 @@
           <t>What is the TOTAL 2025 expense budget (all seven categories) for department D400, Primary Care Clinic, where Dr. Nguyen practices? Use one lookup that returns the department's whole row of the grid, wrapped in SUM.</t>
         </is>
       </c>
-      <c r="C15" s="47" t="n">
+      <c r="C15" s="48" t="n">
         <v>5348882</v>
       </c>
-      <c r="D15" s="45" t="inlineStr">
+      <c r="D15" s="46" t="inlineStr">
         <is>
           <t>=SUM(XLOOKUP("D400",Budget!$A$2:$A$32,Budget!$D$2:$J$32))</t>
         </is>
       </c>
-      <c r="E15" cm="1" s="48">
+      <c r="E15" cm="1" s="49">
         <f t="array" ref="E15">SUM(_xlfn.XLOOKUP("D400",Budget!$A$2:$A$32,Budget!$D$2:$J$32))</f>
         <v/>
       </c>
@@ -20561,15 +20576,15 @@
           <t>Patient PT13163 visited more often than anyone else on the panel (11 encounters in 2025). The Encounters sheet is sorted oldest to newest. Use XLOOKUP searching from the bottom up to return the AdmitDate of this patient's most recent encounter.</t>
         </is>
       </c>
-      <c r="C16" s="49" t="n">
+      <c r="C16" s="50" t="n">
         <v>46020</v>
       </c>
-      <c r="D16" s="45" t="inlineStr">
+      <c r="D16" s="46" t="inlineStr">
         <is>
           <t>=XLOOKUP("PT13163",Encounters!$B$2:$B$530,Encounters!$D$2:$D$530,,0,-1)</t>
         </is>
       </c>
-      <c r="E16" cm="1" s="50">
+      <c r="E16" cm="1" s="51">
         <f t="array" ref="E16">_xlfn.XLOOKUP("PT13163",Encounters!$B$2:$B$530,Encounters!$D$2:$D$530,,0,-1)</f>
         <v/>
       </c>
@@ -20587,18 +20602,18 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>The Referrals sheet lists 24 referrals received in December. Fill its yellow PatientID column by looking up each MRN in the Patients sheet (start in G2). Patients who aren't on the panel yet must show the text Not found instead of #N/A. The gray cell counts the Not found rows.</t>
-        </is>
-      </c>
-      <c r="C17" s="44" t="n">
+          <t>The Referrals sheet lists 24 referrals received in December. Fill its yellow PatientID column by looking up each MRN in the Patients sheet (start in G2 and copy down to row 25). Patients who aren't on the panel yet must show the text Not found instead of #N/A. The gray cell counts the Not found rows.</t>
+        </is>
+      </c>
+      <c r="C17" s="45" t="n">
         <v>7</v>
       </c>
-      <c r="D17" s="45" t="inlineStr">
+      <c r="D17" s="46" t="inlineStr">
         <is>
           <t>=XLOOKUP(C2,Patients!$B$2:$B$186,Patients!$A$2:$A$186,"Not found")</t>
         </is>
       </c>
-      <c r="E17" cm="1" s="46">
+      <c r="E17" cm="1" s="47">
         <f t="array" ref="E17">SUMPRODUCT(--ISNA(MATCH(Referrals!$C$2:$C$25,Patients!$B$2:$B$186,0)))</f>
         <v/>
       </c>
@@ -20636,46 +20651,46 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="41" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>🔑 Bonus Key — Lesson 2.6</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="42" t="inlineStr">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="44" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
+      <c r="D4" s="44" t="inlineStr">
         <is>
           <t>Sample solution</t>
         </is>
       </c>
-      <c r="E4" s="43" t="inlineStr">
+      <c r="E4" s="44" t="inlineStr">
         <is>
           <t>Live result</t>
         </is>
       </c>
-      <c r="F4" s="43" t="inlineStr">
+      <c r="F4" s="44" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -20689,26 +20704,26 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>Card A (ENC117295): what does your Patient name row (Card!B8) show? Format: First Last.</t>
-        </is>
-      </c>
-      <c r="C5" s="44" t="inlineStr">
+          <t>Card 1 (ENC117295): what does your Patient name row (Card!B8) show? Format: First Last.</t>
+        </is>
+      </c>
+      <c r="C5" s="45" t="inlineStr">
         <is>
           <t>Carlos Ortiz</t>
         </is>
       </c>
-      <c r="D5" s="45" t="inlineStr">
+      <c r="D5" s="46" t="inlineStr">
         <is>
           <t>=IF(B6="Not found","Not found",XLOOKUP(B6,Patients!$A$2:$A$186,Patients!$C$2:$C$186)&amp;" "&amp;XLOOKUP(B6,Patients!$A$2:$A$186,Patients!$D$2:$D$186))</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="46">
+      <c r="E5" cm="1" s="47">
         <f t="array" ref="E5">_xlfn.XLOOKUP(_xlfn.XLOOKUP("ENC117295",Encounters!$A$2:$A$530,Encounters!$B$2:$B$530),Patients!$A$2:$A$186,Patients!$C$2:$C$186)&amp;" "&amp;_xlfn.XLOOKUP(_xlfn.XLOOKUP("ENC117295",Encounters!$A$2:$A$530,Encounters!$B$2:$B$530),Patients!$A$2:$A$186,Patients!$D$2:$D$186)</f>
         <v/>
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>Row 6 does the first hop (EncounterID → PatientID) once, and every patient row reuses it. Chaining through a helper cell keeps each formula short and lets you check each hop on its own. The IF in front returns Not found when row 6 already says so, which keeps Card B clean.</t>
+          <t>Row 6 does the first hop, from EncounterID to PatientID, once, and every patient row reuses it. Chaining through a helper cell keeps each formula short and lets you check each hop on its own. The IF in front returns Not found when row 6 already says so, which keeps Card 2 clean.</t>
         </is>
       </c>
     </row>
@@ -20720,18 +20735,18 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>Card A: how old was the patient, in completed years, on the encounter's AdmitDate (Card!B9)?</t>
-        </is>
-      </c>
-      <c r="C6" s="44" t="n">
+          <t>Card 1: how old was the patient, in completed years, on the encounter's AdmitDate (Card!B9)?</t>
+        </is>
+      </c>
+      <c r="C6" s="45" t="n">
         <v>78</v>
       </c>
-      <c r="D6" s="45" t="inlineStr">
+      <c r="D6" s="46" t="inlineStr">
         <is>
           <t>=IF(B6="Not found","Not found",DATEDIF(XLOOKUP(B6,Patients!$A$2:$A$186,Patients!$F$2:$F$186),XLOOKUP(B$5,Encounters!$A$2:$A$530,Encounters!$D$2:$D$530),"Y"))</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="46">
+      <c r="E6" cm="1" s="47">
         <f t="array" ref="E6">DATEDIF(_xlfn.XLOOKUP(_xlfn.XLOOKUP("ENC117295",Encounters!$A$2:$A$530,Encounters!$B$2:$B$530),Patients!$A$2:$A$186,Patients!$F$2:$F$186),_xlfn.XLOOKUP("ENC117295",Encounters!$A$2:$A$530,Encounters!$D$2:$D$530),"Y")</f>
         <v/>
       </c>
@@ -20749,20 +20764,20 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Card A: what does your Attending row (Card!B12) show? Format: First Last, Credential (for example, Isabella Nguyen, MD).</t>
-        </is>
-      </c>
-      <c r="C7" s="44" t="inlineStr">
+          <t>Card 1: what does your Attending row (Card!B12) show? Format: First Last, Credential (for example, Isabella Nguyen, MD).</t>
+        </is>
+      </c>
+      <c r="C7" s="45" t="inlineStr">
         <is>
           <t>Judith Cox, DO</t>
         </is>
       </c>
-      <c r="D7" s="45" t="inlineStr">
+      <c r="D7" s="46" t="inlineStr">
         <is>
           <t>=IF(B7="Not found","Not found",XLOOKUP(B7,Providers!$A$2:$A$148,Providers!$B$2:$B$148)&amp;" "&amp;XLOOKUP(B7,Providers!$A$2:$A$148,Providers!$C$2:$C$148)&amp;", "&amp;XLOOKUP(B7,Providers!$A$2:$A$148,Providers!$D$2:$D$148))</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="46">
+      <c r="E7" cm="1" s="47">
         <f t="array" ref="E7">_xlfn.XLOOKUP(_xlfn.XLOOKUP("ENC117295",Encounters!$A$2:$A$530,Encounters!$G$2:$G$530),Providers!$A$2:$A$148,Providers!$B$2:$B$148)&amp;" "&amp;_xlfn.XLOOKUP(_xlfn.XLOOKUP("ENC117295",Encounters!$A$2:$A$530,Encounters!$G$2:$G$530),Providers!$A$2:$A$148,Providers!$C$2:$C$148)&amp;", "&amp;_xlfn.XLOOKUP(_xlfn.XLOOKUP("ENC117295",Encounters!$A$2:$A$530,Encounters!$G$2:$G$530),Providers!$A$2:$A$148,Providers!$D$2:$D$148)</f>
         <v/>
       </c>
@@ -20780,20 +20795,20 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Card A: what is the claim status (Card!B15)? Claims are matched by EncounterID, which is column B of the Claims sheet.</t>
-        </is>
-      </c>
-      <c r="C8" s="44" t="inlineStr">
+          <t>Card 1: what is the claim status (Card!B15)? Claims are matched by EncounterID, which is column B of the Claims sheet.</t>
+        </is>
+      </c>
+      <c r="C8" s="45" t="inlineStr">
         <is>
           <t>Denied</t>
         </is>
       </c>
-      <c r="D8" s="45" t="inlineStr">
+      <c r="D8" s="46" t="inlineStr">
         <is>
           <t>=XLOOKUP(B$5,Claims!$B$2:$B$530,Claims!$G$2:$G$530,"Not found")</t>
         </is>
       </c>
-      <c r="E8" cm="1" s="46">
+      <c r="E8" cm="1" s="47">
         <f t="array" ref="E8">_xlfn.XLOOKUP("ENC117295",Claims!$B$2:$B$530,Claims!$G$2:$G$530)</f>
         <v/>
       </c>
@@ -20811,18 +20826,18 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Card B (ENC119O88): how many of the ten output rows (Card!C6:C15) show exactly Not found? All ten should. If any shows #N/A or #VALUE!, fix that row's formula in column B and copy it right again.</t>
-        </is>
-      </c>
-      <c r="C9" s="44" t="n">
+          <t>Card 2 (ENC119O88): how many of the ten output rows (Card!C6:C15) show exactly Not found? All ten should. If any shows #N/A or #VALUE!, fix that row's formula in column B and copy it to column C again.</t>
+        </is>
+      </c>
+      <c r="C9" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="D9" s="45" t="inlineStr">
+      <c r="D9" s="46" t="inlineStr">
         <is>
           <t>=XLOOKUP(B$5,Encounters!$A$2:$A$530,Encounters!$B$2:$B$530,"Not found")</t>
         </is>
       </c>
-      <c r="E9" cm="1" s="46">
+      <c r="E9" cm="1" s="47">
         <f t="array" ref="E9">IF(ISNA(MATCH("ENC119O88",Encounters!$A$2:$A$530,0)),10,0)</f>
         <v/>
       </c>
@@ -20833,7 +20848,7 @@
 2. Chained lookups pass "Not found" along. The inner XLOOKUP returns it, and the outer one can't find a DxCode called "Not found", so it returns its own "Not found".
 3. Rows that join or calculate (the two name rows and the age row) test their helper cell first with IF(B6="Not found","Not found",…). Without that test, DATEDIF of the text "Not found" returns #VALUE!. A name join would show #N/A, or "Not found Not found" if each of its lookups had its own if_not_found.
 Your finished card should match this:
-| Row | Field | Card A (ENC117295) | Card B (ENC119O88) |
+| Row | Field | Card 1 (ENC117295) | Card 2 (ENC119O88) |
 |:-:|---|---|---|
 | 6 | PatientID | PT12752 | Not found |
 | 7 | Attending ProviderID | PRV1030 | Not found |
@@ -20892,10 +20907,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="49" customHeight="1">
+    <row r="2" ht="79" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>The Encounters sheet stores IDs only. Every answer comes from looking an ID up in another sheet. Write each answer as a formula. Your answers sit on this Practice sheet, so a reference to a data cell needs its sheet name, such as Encounters!B9. Click the cell on the data sheet and Excel writes the sheet name for you. Lock lookup ranges with $ (F4, Mac: ⌘ + T) so they don't slide when you copy.</t>
+          <t>The Encounters sheet stores IDs only, so every answer comes from looking an ID up in another sheet. Write each answer as a formula. Your answers sit on this Practice sheet, so a reference to a data cell needs its sheet name, such as Encounters!B9. Click the cell on the data sheet and Excel writes the sheet name for you. Tasks 5, 7, and 13 are different: you type the formula on a data sheet and copy it down the column, and the gray cell here reads your column. Lock the lookup table's ranges with $ (F4, Mac: ⌘ + T) so they don't slide when you copy. If Excel writes a Table reference such as tblPayers[PayerName] instead, keep it, because a Table reference never slides when you copy it down.</t>
         </is>
       </c>
     </row>
@@ -21217,7 +21232,7 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>The Referrals sheet lists 24 referrals received in December. Fill its yellow PatientID column by looking up each MRN in the Patients sheet (start in G2). Patients who aren't on the panel yet must show the text Not found instead of #N/A. The gray cell counts the Not found rows.</t>
+          <t>The Referrals sheet lists 24 referrals received in December. Fill its yellow PatientID column by looking up each MRN in the Patients sheet (start in G2 and copy down to row 25). Patients who aren't on the panel yet must show the text Not found instead of #N/A. The gray cell counts the Not found rows.</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -61495,7 +61510,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="75" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>

--- a/02-formulas-functions/06-lookup-functions/2.6-lookup-functions.xlsx
+++ b/02-formulas-functions/06-lookup-functions/2.6-lookup-functions.xlsx
@@ -227,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -325,20 +325,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1024,7 +1021,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="33" customHeight="1">
+    <row r="15" ht="18" customHeight="1">
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>3. Check yourself</t>
@@ -1032,7 +1029,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red). Tasks marked 'See key' are checked by comparing with the answer key.</t>
+          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red).</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1145,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Pre-filled summary formula — it reads the work you did on another sheet.</t>
+          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1169,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Not matching yet — check the hint and try again.</t>
+          <t>Not matching yet. Check the hint and try again.</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1189,7 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Data: 529 rows — Excel Table 'tblEncounters'</t>
+          <t>Data: 529 rows, in the Excel Table 'tblEncounters'</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1201,7 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Data: 185 rows — Excel Table 'tblPatients'</t>
+          <t>Data: 185 rows, in the Excel Table 'tblPatients'</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1213,7 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Data: 24 rows — Excel Table 'tblReferrals'</t>
+          <t>Data: 24 rows, in the Excel Table 'tblReferrals'</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1225,7 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Data: 147 rows — Excel Table 'tblProviders'</t>
+          <t>Data: 147 rows, in the Excel Table 'tblProviders'</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1237,7 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Data: 51 rows — Excel Table 'tblDiagnoses'</t>
+          <t>Data: 51 rows, in the Excel Table 'tblDiagnoses'</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1249,7 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Data: 8 rows — Excel Table 'tblPayers'</t>
+          <t>Data: 8 rows, in the Excel Table 'tblPayers'</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1261,7 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Data: 31 rows — Excel Table 'tblDepartments'</t>
+          <t>Data: 31 rows, in the Excel Table 'tblDepartments'</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1273,7 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Data: 529 rows — Excel Table 'tblClaims'</t>
+          <t>Data: 529 rows, in the Excel Table 'tblClaims'</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1285,7 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Data: 31 rows — Excel Table 'tblBudget'</t>
+          <t>Data: 31 rows, in the Excel Table 'tblBudget'</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1297,7 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Data: 6 rows — Excel Table 'tblBMITiers'</t>
+          <t>Data: 6 rows, in the Excel Table 'tblBMITiers'</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1309,7 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Data: 6 rows — Excel Table 'tblAgeBands'</t>
+          <t>Data: 6 rows, in the Excel Table 'tblAgeBands'</t>
         </is>
       </c>
     </row>
@@ -20182,7 +20179,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -20196,7 +20193,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="43" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -20253,7 +20250,7 @@
           <t>=VLOOKUP(Encounters!B9,Patients!$A$2:$K$186,4,FALSE)</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="47">
+      <c r="E5" cm="1" s="19">
         <f t="array" ref="E5">VLOOKUP(Encounters!B9,Patients!$A$2:$K$186,4,FALSE)</f>
         <v/>
       </c>
@@ -20284,7 +20281,7 @@
           <t>=VLOOKUP(Encounters!I20,Payers!$A$2:$F$9,3,FALSE)</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="47">
+      <c r="E6" cm="1" s="19">
         <f t="array" ref="E6">VLOOKUP(Encounters!I20,Payers!$A$2:$F$9,3,FALSE)</f>
         <v/>
       </c>
@@ -20315,7 +20312,7 @@
           <t>=XLOOKUP(Encounters!H150,Diagnoses!$A$2:$A$52,Diagnoses!$B$2:$B$52)</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="47">
+      <c r="E7" cm="1" s="19">
         <f t="array" ref="E7">_xlfn.XLOOKUP(Encounters!H150,Diagnoses!$A$2:$A$52,Diagnoses!$B$2:$B$52)</f>
         <v/>
       </c>
@@ -20346,7 +20343,7 @@
           <t>=INDEX(Providers!$E$2:$E$148,MATCH(Encounters!G73,Providers!$A$2:$A$148,0))</t>
         </is>
       </c>
-      <c r="E8" cm="1" s="47">
+      <c r="E8" cm="1" s="19">
         <f t="array" ref="E8">INDEX(Providers!$E$2:$E$148,MATCH(Encounters!G73,Providers!$A$2:$A$148,0))</f>
         <v/>
       </c>
@@ -20375,7 +20372,7 @@
           <t>=XLOOKUP(I2,Payers!$A$2:$A$9,Payers!$B$2:$B$9)</t>
         </is>
       </c>
-      <c r="E9" cm="1" s="47">
+      <c r="E9" cm="1" s="19">
         <f t="array" ref="E9">COUNTIF(Encounters!$I$2:$I$530,"PY01")</f>
         <v/>
       </c>
@@ -20406,7 +20403,7 @@
           <t>=VLOOKUP(Patients!G21,AgeBands!$A$2:$B$7,2,TRUE)</t>
         </is>
       </c>
-      <c r="E10" cm="1" s="47">
+      <c r="E10" cm="1" s="19">
         <f t="array" ref="E10">VLOOKUP(Patients!G21,AgeBands!$A$2:$B$7,2,TRUE)</f>
         <v/>
       </c>
@@ -20435,7 +20432,7 @@
           <t>=VLOOKUP(J2,BMITiers!$A$2:$B$7,2,TRUE)</t>
         </is>
       </c>
-      <c r="E11" cm="1" s="47">
+      <c r="E11" cm="1" s="19">
         <f t="array" ref="E11">COUNTIF(Patients!$J$2:$J$186,"&gt;=30")</f>
         <v/>
       </c>
@@ -20466,7 +20463,7 @@
           <t>=XLOOKUP(TEXT(50339,"00000000"),Patients!$B$2:$B$186,Patients!$A$2:$A$186)</t>
         </is>
       </c>
-      <c r="E12" cm="1" s="47">
+      <c r="E12" cm="1" s="19">
         <f t="array" ref="E12">_xlfn.XLOOKUP(TEXT(50339,"00000000"),Patients!$B$2:$B$186,Patients!$A$2:$A$186)</f>
         <v/>
       </c>
@@ -20497,13 +20494,13 @@
           <t>=XLOOKUP("*knee*",Diagnoses!$B$2:$B$52,Diagnoses!$A$2:$A$52,,2)</t>
         </is>
       </c>
-      <c r="E13" cm="1" s="47">
+      <c r="E13" cm="1" s="19">
         <f t="array" ref="E13">_xlfn.XLOOKUP("*knee*",Diagnoses!$B$2:$B$52,Diagnoses!$A$2:$A$52,,2)</f>
         <v/>
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>The asterisk stands for any number of characters, so "*knee*" matches "Unilateral primary osteoarthritis, right knee". XLOOKUP only uses wildcards when match_mode is 2. MATCH with match_type 0 uses them automatically: =INDEX(Diagnoses!$A$2:$A$52,MATCH("*knee*",Diagnoses!$B$2:$B$52,0)). If several descriptions matched, you'd get the first one.</t>
+          <t>The asterisk stands for any number of characters, so "knee" matches "Unilateral primary osteoarthritis, right knee". XLOOKUP only uses wildcards when match_mode is 2. MATCH with match_type 0 uses them automatically: =INDEX(Diagnoses!$A$2:$A$52,MATCH("knee",Diagnoses!$B$2:$B$52,0)). If several descriptions matched, you'd get the first one.</t>
         </is>
       </c>
     </row>
@@ -20518,7 +20515,7 @@
           <t>Two-way lookup: on the Budget sheet, what is the 2025 Pharmaceuticals budget for department D130 (Intensive Care Unit at Bluestone Memorial Hospital)? Find the row by DeptID and the column by category name.</t>
         </is>
       </c>
-      <c r="C14" s="48" t="n">
+      <c r="C14" s="47" t="n">
         <v>993601</v>
       </c>
       <c r="D14" s="46" t="inlineStr">
@@ -20526,7 +20523,7 @@
           <t>=INDEX(Budget!$D$2:$J$32,MATCH("D130",Budget!$A$2:$A$32,0),MATCH("Pharmaceuticals",Budget!$D$1:$J$1,0))</t>
         </is>
       </c>
-      <c r="E14" cm="1" s="49">
+      <c r="E14" cm="1" s="48">
         <f t="array" ref="E14">INDEX(Budget!$D$2:$J$32,MATCH("D130",Budget!$A$2:$A$32,0),MATCH("Pharmaceuticals",Budget!$D$1:$J$1,0))</f>
         <v/>
       </c>
@@ -20547,7 +20544,7 @@
           <t>What is the TOTAL 2025 expense budget (all seven categories) for department D400, Primary Care Clinic, where Dr. Nguyen practices? Use one lookup that returns the department's whole row of the grid, wrapped in SUM.</t>
         </is>
       </c>
-      <c r="C15" s="48" t="n">
+      <c r="C15" s="47" t="n">
         <v>5348882</v>
       </c>
       <c r="D15" s="46" t="inlineStr">
@@ -20555,7 +20552,7 @@
           <t>=SUM(XLOOKUP("D400",Budget!$A$2:$A$32,Budget!$D$2:$J$32))</t>
         </is>
       </c>
-      <c r="E15" cm="1" s="49">
+      <c r="E15" cm="1" s="48">
         <f t="array" ref="E15">SUM(_xlfn.XLOOKUP("D400",Budget!$A$2:$A$32,Budget!$D$2:$J$32))</f>
         <v/>
       </c>
@@ -20576,7 +20573,7 @@
           <t>Patient PT13163 visited more often than anyone else on the panel (11 encounters in 2025). The Encounters sheet is sorted oldest to newest. Use XLOOKUP searching from the bottom up to return the AdmitDate of this patient's most recent encounter.</t>
         </is>
       </c>
-      <c r="C16" s="50" t="n">
+      <c r="C16" s="49" t="n">
         <v>46020</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
@@ -20584,7 +20581,7 @@
           <t>=XLOOKUP("PT13163",Encounters!$B$2:$B$530,Encounters!$D$2:$D$530,,0,-1)</t>
         </is>
       </c>
-      <c r="E16" cm="1" s="51">
+      <c r="E16" cm="1" s="50">
         <f t="array" ref="E16">_xlfn.XLOOKUP("PT13163",Encounters!$B$2:$B$530,Encounters!$D$2:$D$530,,0,-1)</f>
         <v/>
       </c>
@@ -20613,7 +20610,7 @@
           <t>=XLOOKUP(C2,Patients!$B$2:$B$186,Patients!$A$2:$A$186,"Not found")</t>
         </is>
       </c>
-      <c r="E17" cm="1" s="47">
+      <c r="E17" cm="1" s="19">
         <f t="array" ref="E17">SUMPRODUCT(--ISNA(MATCH(Referrals!$C$2:$C$25,Patients!$B$2:$B$186,0)))</f>
         <v/>
       </c>
@@ -20646,7 +20643,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -20660,7 +20657,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="43" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -20717,7 +20714,7 @@
           <t>=IF(B6="Not found","Not found",XLOOKUP(B6,Patients!$A$2:$A$186,Patients!$C$2:$C$186)&amp;" "&amp;XLOOKUP(B6,Patients!$A$2:$A$186,Patients!$D$2:$D$186))</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="47">
+      <c r="E5" cm="1" s="19">
         <f t="array" ref="E5">_xlfn.XLOOKUP(_xlfn.XLOOKUP("ENC117295",Encounters!$A$2:$A$530,Encounters!$B$2:$B$530),Patients!$A$2:$A$186,Patients!$C$2:$C$186)&amp;" "&amp;_xlfn.XLOOKUP(_xlfn.XLOOKUP("ENC117295",Encounters!$A$2:$A$530,Encounters!$B$2:$B$530),Patients!$A$2:$A$186,Patients!$D$2:$D$186)</f>
         <v/>
       </c>
@@ -20746,7 +20743,7 @@
           <t>=IF(B6="Not found","Not found",DATEDIF(XLOOKUP(B6,Patients!$A$2:$A$186,Patients!$F$2:$F$186),XLOOKUP(B$5,Encounters!$A$2:$A$530,Encounters!$D$2:$D$530),"Y"))</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="47">
+      <c r="E6" cm="1" s="19">
         <f t="array" ref="E6">DATEDIF(_xlfn.XLOOKUP(_xlfn.XLOOKUP("ENC117295",Encounters!$A$2:$A$530,Encounters!$B$2:$B$530),Patients!$A$2:$A$186,Patients!$F$2:$F$186),_xlfn.XLOOKUP("ENC117295",Encounters!$A$2:$A$530,Encounters!$D$2:$D$530),"Y")</f>
         <v/>
       </c>
@@ -20777,7 +20774,7 @@
           <t>=IF(B7="Not found","Not found",XLOOKUP(B7,Providers!$A$2:$A$148,Providers!$B$2:$B$148)&amp;" "&amp;XLOOKUP(B7,Providers!$A$2:$A$148,Providers!$C$2:$C$148)&amp;", "&amp;XLOOKUP(B7,Providers!$A$2:$A$148,Providers!$D$2:$D$148))</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="47">
+      <c r="E7" cm="1" s="19">
         <f t="array" ref="E7">_xlfn.XLOOKUP(_xlfn.XLOOKUP("ENC117295",Encounters!$A$2:$A$530,Encounters!$G$2:$G$530),Providers!$A$2:$A$148,Providers!$B$2:$B$148)&amp;" "&amp;_xlfn.XLOOKUP(_xlfn.XLOOKUP("ENC117295",Encounters!$A$2:$A$530,Encounters!$G$2:$G$530),Providers!$A$2:$A$148,Providers!$C$2:$C$148)&amp;", "&amp;_xlfn.XLOOKUP(_xlfn.XLOOKUP("ENC117295",Encounters!$A$2:$A$530,Encounters!$G$2:$G$530),Providers!$A$2:$A$148,Providers!$D$2:$D$148)</f>
         <v/>
       </c>
@@ -20808,7 +20805,7 @@
           <t>=XLOOKUP(B$5,Claims!$B$2:$B$530,Claims!$G$2:$G$530,"Not found")</t>
         </is>
       </c>
-      <c r="E8" cm="1" s="47">
+      <c r="E8" cm="1" s="19">
         <f t="array" ref="E8">_xlfn.XLOOKUP("ENC117295",Claims!$B$2:$B$530,Claims!$G$2:$G$530)</f>
         <v/>
       </c>
@@ -20837,7 +20834,7 @@
           <t>=XLOOKUP(B$5,Encounters!$A$2:$A$530,Encounters!$B$2:$B$530,"Not found")</t>
         </is>
       </c>
-      <c r="E9" cm="1" s="47">
+      <c r="E9" cm="1" s="19">
         <f t="array" ref="E9">IF(ISNA(MATCH("ENC119O88",Encounters!$A$2:$A$530,0)),10,0)</f>
         <v/>
       </c>

--- a/02-formulas-functions/06-lookup-functions/2.6-lookup-functions.xlsx
+++ b/02-formulas-functions/06-lookup-functions/2.6-lookup-functions.xlsx
@@ -904,7 +904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C43"/>
+  <dimension ref="B2:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -929,7 +929,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Beginner → Intermediate  ·  about 60 minutes  ·  Bluestone Health System (fictional)</t>
+          <t>Beginner → Intermediate  ·  about 125 minutes  ·  Bluestone Health System (fictional)</t>
         </is>
       </c>
     </row>
@@ -1184,154 +1184,178 @@
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Encounters</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Data: 529 rows, in the Excel Table 'tblEncounters'</t>
+          <t>13 practice tasks, each with a Check cell.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Patients</t>
+          <t>Encounters</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Data: 185 rows, in the Excel Table 'tblPatients'</t>
+          <t>Data: 529 rows, in the Excel Table 'tblEncounters'</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>Patients</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Data: 24 rows, in the Excel Table 'tblReferrals'</t>
+          <t>Data: 185 rows, in the Excel Table 'tblPatients'</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Providers</t>
+          <t>Referrals</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Data: 147 rows, in the Excel Table 'tblProviders'</t>
+          <t>Data: 24 rows, in the Excel Table 'tblReferrals'</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Diagnoses</t>
+          <t>Providers</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Data: 51 rows, in the Excel Table 'tblDiagnoses'</t>
+          <t>Data: 147 rows, in the Excel Table 'tblProviders'</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Payers</t>
+          <t>Diagnoses</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Data: 8 rows, in the Excel Table 'tblPayers'</t>
+          <t>Data: 51 rows, in the Excel Table 'tblDiagnoses'</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Departments</t>
+          <t>Payers</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Data: 31 rows, in the Excel Table 'tblDepartments'</t>
+          <t>Data: 8 rows, in the Excel Table 'tblPayers'</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Claims</t>
+          <t>Departments</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Data: 529 rows, in the Excel Table 'tblClaims'</t>
+          <t>Data: 31 rows, in the Excel Table 'tblDepartments'</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Budget</t>
+          <t>Claims</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Data: 31 rows, in the Excel Table 'tblBudget'</t>
+          <t>Data: 529 rows, in the Excel Table 'tblClaims'</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>BMITiers</t>
+          <t>Budget</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Data: 6 rows, in the Excel Table 'tblBMITiers'</t>
+          <t>Data: 31 rows, in the Excel Table 'tblBudget'</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="8" t="inlineStr">
         <is>
+          <t>BMITiers</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Data: 6 rows, in the Excel Table 'tblBMITiers'</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
           <t>AgeBands</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>Data: 6 rows, in the Excel Table 'tblAgeBands'</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="63" customHeight="1">
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>About the data</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>Every 2025 encounter (529) for the 185 patients on Dr. Isabella Nguyen's internal medicine panel, stored as IDs only, plus the lookup tables that turn those IDs into names: the panel roster, providers, ICD-10 diagnoses, payers, departments, and claims. Also a 2025 department budget grid, BMI and age-band tier tables, and the practice's December 2025 referral list.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="8" t="inlineStr">
         <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>The bonus challenge (5 parts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="63" customHeight="1">
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>About the data</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Every 2025 encounter (529) for the 185 patients on Dr. Isabella Nguyen's internal medicine panel, stored as IDs only, plus the lookup tables that turn those IDs into names: the panel roster, providers, ICD-10 diagnoses, payers, departments, and claims. Also a 2025 department budget grid, BMI and age-band tier tables, and the practice's December 2025 referral list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="8" t="inlineStr">
+        <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>

--- a/02-formulas-functions/06-lookup-functions/2.6-lookup-functions.xlsx
+++ b/02-formulas-functions/06-lookup-functions/2.6-lookup-functions.xlsx
@@ -1009,7 +1009,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="48" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>2. Practice</t>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Go to the 'Practice' sheet. Type a formula or value into each yellow cell.</t>
+          <t>Go to the 'Practice' sheet. Type a formula or value into each yellow cell. For tasks 5, 7, and 13, fill the yellow column on the Encounters, Patients, or Referrals sheet instead, and the task's gray cell on Practice reads it.</t>
         </is>
       </c>
     </row>
@@ -1105,235 +1105,235 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>The Card sheet is for the bonus challenge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="4" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Color legend</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Yellow cell</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Your answer goes here.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Yellow cell</t>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Gray cell</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Your answer goes here.</t>
+          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>Gray cell</t>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>✔ Correct</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
+          <t>Your answer matches the key.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>✔ Correct</t>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>✘ Not yet</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Your answer matches the key.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>✘ Not yet</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
           <t>Not matching yet. Check the hint and try again.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="4" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Sheets in this workbook</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>13 practice tasks, each with a Check cell.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Practice</t>
+          <t>Encounters</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>13 practice tasks, each with a Check cell.</t>
+          <t>Data: 529 rows, in the Excel Table 'tblEncounters'</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Encounters</t>
+          <t>Patients</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Data: 529 rows, in the Excel Table 'tblEncounters'</t>
+          <t>Data: 185 rows, in the Excel Table 'tblPatients'</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Patients</t>
+          <t>Referrals</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Data: 185 rows, in the Excel Table 'tblPatients'</t>
+          <t>Data: 24 rows, in the Excel Table 'tblReferrals'</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>Providers</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Data: 24 rows, in the Excel Table 'tblReferrals'</t>
+          <t>Data: 147 rows, in the Excel Table 'tblProviders'</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Providers</t>
+          <t>Diagnoses</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Data: 147 rows, in the Excel Table 'tblProviders'</t>
+          <t>Data: 51 rows, in the Excel Table 'tblDiagnoses'</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Diagnoses</t>
+          <t>Payers</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Data: 51 rows, in the Excel Table 'tblDiagnoses'</t>
+          <t>Data: 8 rows, in the Excel Table 'tblPayers'</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Payers</t>
+          <t>Departments</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Data: 8 rows, in the Excel Table 'tblPayers'</t>
+          <t>Data: 31 rows, in the Excel Table 'tblDepartments'</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Departments</t>
+          <t>Claims</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Data: 31 rows, in the Excel Table 'tblDepartments'</t>
+          <t>Data: 529 rows, in the Excel Table 'tblClaims'</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Claims</t>
+          <t>Budget</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Data: 529 rows, in the Excel Table 'tblClaims'</t>
+          <t>Data: 31 rows, in the Excel Table 'tblBudget'</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Budget</t>
+          <t>BMITiers</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Data: 31 rows, in the Excel Table 'tblBudget'</t>
+          <t>Data: 6 rows, in the Excel Table 'tblBMITiers'</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>BMITiers</t>
+          <t>AgeBands</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Data: 6 rows, in the Excel Table 'tblBMITiers'</t>
+          <t>Data: 6 rows, in the Excel Table 'tblAgeBands'</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>AgeBands</t>
+          <t>Bonus</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Data: 6 rows, in the Excel Table 'tblAgeBands'</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
+          <t>The bonus challenge (5 parts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="33" customHeight="1">
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Bonus</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>The bonus challenge (5 parts).</t>
+          <t>The bonus encounter lookup card. Type one formula in each yellow cell of column B (rows 6–15), then copy them to column C. The Bonus sheet's gray cells read it.</t>
         </is>
       </c>
     </row>
@@ -19785,7 +19785,7 @@
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Type a formula or value in each yellow cell. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Bonus Key'.</t>
+          <t>There's nothing to type on this sheet. Build the card in the yellow cells on the Card sheet, and the gray cells here read it. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Bonus Key'.</t>
         </is>
       </c>
     </row>
